--- a/output/pdf_financials_xlsx/RVV.xlsx
+++ b/output/pdf_financials_xlsx/RVV.xlsx
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.071793</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.045576</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00136</v>
       </c>
     </row>
     <row r="13">
@@ -863,13 +863,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-6.3209</v>
+        <v>-6.249107</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-5.618622</v>
+        <v>-5.573046</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-11.011319</v>
+        <v>-11.009959</v>
       </c>
     </row>
     <row r="28">
@@ -895,13 +895,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-6.320466</v>
+        <v>-6.248673</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-5.618294</v>
+        <v>-5.572718</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-11.011071</v>
+        <v>-11.009711</v>
       </c>
     </row>
     <row r="30">
@@ -2425,13 +2425,13 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.152036</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.154573</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.025848</v>
       </c>
     </row>
     <row r="125">
@@ -2441,13 +2441,13 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.152036</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.154573</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.025848</v>
       </c>
     </row>
     <row r="126">
@@ -4200,7 +4200,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E51" s="5" t="n">
         <v>-0.152036</v>
       </c>
@@ -4920,7 +4924,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E75" s="5" t="n">

--- a/output/pdf_financials_xlsx/RVV.xlsx
+++ b/output/pdf_financials_xlsx/RVV.xlsx
@@ -529,13 +529,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.918436</v>
+        <v>1.536154</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1.364166</v>
+        <v>1.785054</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.819589</v>
+        <v>1.083901</v>
       </c>
     </row>
     <row r="8">
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.918436</v>
+        <v>1.536154</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1.364166</v>
+        <v>1.785054</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.819589</v>
+        <v>1.083901</v>
       </c>
     </row>
     <row r="11">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.918436</v>
+        <v>-1.536154</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-1.364166</v>
+        <v>-1.785054</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.819589</v>
+        <v>-1.083901</v>
       </c>
     </row>
     <row r="12">
@@ -1512,13 +1512,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.6386849999999999</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.718403</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.866161</v>
       </c>
     </row>
     <row r="68">
@@ -2051,13 +2051,13 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>0.059735</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>0.010648</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>0.008101000000000001</v>
       </c>
     </row>
     <row r="102">
@@ -2131,13 +2131,13 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-0.757348</v>
+        <v>-0.697613</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-0.196187</v>
+        <v>-0.185539</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.541797</v>
+        <v>0.549898</v>
       </c>
     </row>
     <row r="107">
@@ -3898,7 +3898,11 @@
           <t>HST receivable</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E41" s="5" t="n">
         <v>0.059735</v>
       </c>
@@ -4684,7 +4688,11 @@
           <t>Office expenses (note 22)</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E67" s="5" t="n">
         <v>0.617718</v>
       </c>
